--- a/basedatos_partidas/salida/descompuestos/CT-17-03-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-17-03-030.xlsx
@@ -539,10 +539,10 @@
         <v>1.2</v>
       </c>
       <c r="G10" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="H10" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="11">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.78</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="13">
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>10.43</v>
+        <v>10.16</v>
       </c>
       <c r="H21" t="n">
         <v>0.1</v>
@@ -743,7 +743,7 @@
       </c>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="5" t="n">
-        <v>10.53</v>
+        <v>10.26</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-17-03-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-17-03-030.xlsx
@@ -565,10 +565,10 @@
         <v>0.14</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H11" t="n">
-        <v>1.96</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="12">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.51</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="13">
@@ -724,10 +724,10 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>10.16</v>
+        <v>14.92</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="22">
@@ -743,7 +743,7 @@
       </c>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="5" t="n">
-        <v>10.26</v>
+        <v>15.07</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-17-03-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-17-03-030.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 17 Equipamiento y mobiliario fijo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Mobiliario de baño</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-17-03-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-17-03-030.xlsx
@@ -478,14 +478,14 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Encimera de baño sobre mueble o estructura.</t>
+          <t>Mesón de baño sobre mueble o estructura.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suministro e instalación de encimera de baño en piedra, cuarzo o material compacto, sobre mueble o estructura, con el recorte del lavamanos y su canto trabajado. Incluye la plantilla en obra sobre el mueble ya instalado, el mecanizado del recorte según sea lavamanos sobrepuesto, empotrado o bajo encimera, el presentado y nivelado, el sellado del canto de corte y el sellado perimetral contra la pared. El material lo elige el cliente y se presupuesta aparte. Medido en longitud de encimera.
+          <t xml:space="preserve">Suministro e instalación de mesón de baño en piedra, cuarzo o material compacto, sobre mueble o estructura, con el recorte del lavamanos y su canto trabajado. Incluye la plantilla en obra sobre el mueble ya instalado, el mecanizado del recorte según sea lavamanos sobrepuesto, empotrado o bajo mesón, el presentado y nivelado, el sellado del canto de corte y el sellado perimetral contra la pared. El material lo elige el cliente y se presupuesta aparte. Medido en longitud de mesón.
 </t>
         </is>
       </c>
@@ -654,7 +654,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MO-OF1-SOL</t>
+          <t>MO-OF1-PISO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Oficial de 1ª solador.</t>
+          <t>Oficial de 1ª colocador de pisos.</t>
         </is>
       </c>
       <c r="F17" t="n">
